--- a/artfynd/A 15804-2026 artfynd.xlsx
+++ b/artfynd/A 15804-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>132318220</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2026 artfynd.xlsx
+++ b/artfynd/A 15804-2026 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>132318220</v>
       </c>
       <c r="B3" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 15804-2026 artfynd.xlsx
+++ b/artfynd/A 15804-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126031846</v>
+        <v>132318220</v>
       </c>
       <c r="B2" t="n">
-        <v>98397</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223621</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnattviol</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. latiflora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Drejer) Løjtnant</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,28 +708,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sirsjön, N om, Nrk</t>
+          <t>Svartå, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>470689</v>
+        <v>470552</v>
       </c>
       <c r="R2" t="n">
-        <v>6553336</v>
+        <v>6553492</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,56 +763,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132318220</v>
+        <v>126031846</v>
       </c>
       <c r="B3" t="n">
-        <v>57954</v>
+        <v>99155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>223621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsnattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia subsp. latiflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Drejer) Løjtnant</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,16 +814,28 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartå, Nrk</t>
+          <t>Sirsjön, N om, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>470552</v>
+        <v>470689</v>
       </c>
       <c r="R3" t="n">
-        <v>6553492</v>
+        <v>6553336</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,17 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,18 +876,24 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
